--- a/docs/specs/IM-110操作表示一覧_20260507.xlsx
+++ b/docs/specs/IM-110操作表示一覧_20260507.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/masegi/workspace/IM-110-system/docs/specs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D49CB0-F730-7C4D-B236-6A27EACAFDC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{143F284D-E96D-134B-A469-B8B61C86929B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3100" yWindow="800" windowWidth="31500" windowHeight="19620" activeTab="1" xr2:uid="{C221FF4F-915A-004C-9530-71A2C2B86B23}"/>
+    <workbookView xWindow="3100" yWindow="800" windowWidth="31500" windowHeight="19620" xr2:uid="{C221FF4F-915A-004C-9530-71A2C2B86B23}"/>
   </bookViews>
   <sheets>
     <sheet name="1．測定" sheetId="5" r:id="rId1"/>
@@ -946,23 +946,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>515600</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>158182</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>842172</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>189932</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>84443</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>401943</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>237596</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="75" name="図 74">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C6C7074-32ED-FD46-8D4D-18C0767E473E}"/>
+        <xdr:cNvPr id="76" name="図 75">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{644EE47A-2275-CE46-BFC1-6ED39AC82D12}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -984,8 +984,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7272000" y="13213782"/>
-          <a:ext cx="5152572" cy="3079750"/>
+          <a:off x="15527643" y="8178800"/>
+          <a:ext cx="5143500" cy="3082396"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -997,138 +997,6 @@
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>84443</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>203200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>401943</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>237596</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="76" name="図 75">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{644EE47A-2275-CE46-BFC1-6ED39AC82D12}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="15527643" y="8178800"/>
-          <a:ext cx="5143500" cy="3082396"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>279400</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>124124</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>254000</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>22524</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="78" name="角丸四角形吹き出し 77">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28CD40FF-D2A9-2F48-8322-F319F696F541}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1244600" y="14195724"/>
-          <a:ext cx="5765800" cy="1930400"/>
-        </a:xfrm>
-        <a:prstGeom prst="wedgeRoundRectCallout">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val 60665"/>
-            <a:gd name="adj2" fmla="val -44784"/>
-            <a:gd name="adj3" fmla="val 16667"/>
-          </a:avLst>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800" b="1"/>
-            <a:t>選択式 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2800" b="1"/>
-            <a:t>No.+1</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2800" b="1"/>
-            <a:t>1--&gt;2--&gt;…29--&gt;30--&gt;1</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800" b="1"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
@@ -2162,7 +2030,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2649,7 +2517,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2692,6 +2560,57 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4959FBE-EC2A-5BC1-FF2E-180D82758E49}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7594600" y="23952200"/>
+          <a:ext cx="5080000" cy="3048000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>736600</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="117" name="図 116">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C088BF26-F0F8-509D-35E8-EA6DAC15DD15}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2707,7 +2626,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7594600" y="23952200"/>
+          <a:off x="7493000" y="18821400"/>
           <a:ext cx="5080000" cy="3048000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2715,9 +2634,7 @@
         </a:prstGeom>
         <a:ln>
           <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
+            <a:schemeClr val="tx1"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
@@ -2727,22 +2644,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>736600</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:colOff>711200</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="117" name="図 116">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C088BF26-F0F8-509D-35E8-EA6DAC15DD15}"/>
+        <xdr:cNvPr id="118" name="図 117">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{620DCD04-A310-1BE7-B271-61228CCF1309}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2752,55 +2669,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7493000" y="18821400"/>
-          <a:ext cx="5080000" cy="3048000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>711200</xdr:colOff>
-      <xdr:row>104</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>116</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="118" name="図 117">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{620DCD04-A310-1BE7-B271-61228CCF1309}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3068,7 +2936,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3276,7 +3144,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3399,6 +3267,124 @@
             <a:t>--&gt;</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>787400</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7470681-0D28-7D41-95E6-3F3330A25897}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7289800" y="13563600"/>
+          <a:ext cx="5080000" cy="3048000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>279400</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>124124</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>254000</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>22524</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="78" name="角丸四角形吹き出し 77">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28CD40FF-D2A9-2F48-8322-F319F696F541}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1244600" y="14195724"/>
+          <a:ext cx="5765800" cy="1930400"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 60665"/>
+            <a:gd name="adj2" fmla="val -44784"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800" b="1" u="sng">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>桁選択とインクリメント式</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
